--- a/output/UserRepository.xlsx
+++ b/output/UserRepository.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="151">
   <si>
     <t>Repository</t>
   </si>
@@ -572,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
@@ -740,30 +740,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true">
       <alignment wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -5163,316 +5139,64 @@
       <c r="G187" s="73"/>
       <c r="H187" s="74"/>
     </row>
-    <row r="188" ht="15.0" customHeight="true">
+    <row r="188">
       <c r="A188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C188" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H188" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="189" ht="15.0" customHeight="true">
+    </row>
+    <row r="189">
       <c r="A189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C189" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H189" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" ht="15.0" customHeight="true">
+    </row>
+    <row r="190">
       <c r="A190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C190" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H190" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" ht="15.0" customHeight="true">
+    </row>
+    <row r="191">
       <c r="A191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C191" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H191" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="192" ht="15.0" customHeight="true">
+    </row>
+    <row r="192">
       <c r="A192" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H192" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="193" ht="15.0" customHeight="true">
+    </row>
+    <row r="193">
       <c r="A193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C193" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H193" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="194" ht="15.0" customHeight="true">
+    </row>
+    <row r="194">
       <c r="A194" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C194" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D194" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G194" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H194" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="195" ht="15.0" customHeight="true">
+    </row>
+    <row r="195">
       <c r="A195" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B195" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C195" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E195" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F195" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G195" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H195" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="196" ht="15.0" customHeight="true">
+    </row>
+    <row r="196">
       <c r="A196" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C196" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D196" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E196" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G196" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H196" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="197" ht="15.0" customHeight="true">
+    </row>
+    <row r="197">
       <c r="A197" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C197" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D197" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G197" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H197" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="198" ht="15.0" customHeight="true">
+    </row>
+    <row r="198">
       <c r="A198" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B198" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D198" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G198" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H198" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="199" ht="15.0" customHeight="true">
+    </row>
+    <row r="199">
       <c r="A199" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C199" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="D199" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E199" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G199" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H199" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/UserRepository.xlsx
+++ b/output/UserRepository.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="153">
   <si>
     <t>Repository</t>
   </si>
@@ -20,10 +20,16 @@
     <t>Repository概要</t>
   </si>
   <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Method概要</t>
+    <t>SQL_ID</t>
+  </si>
+  <si>
+    <t>SQL概要</t>
+  </si>
+  <si>
+    <t>selectXX</t>
+  </si>
+  <si>
+    <t>XXを取得する</t>
   </si>
   <si>
     <t>区分</t>
@@ -50,6 +56,12 @@
     <t>備考</t>
   </si>
   <si>
+    <t>●INPUT</t>
+  </si>
+  <si>
+    <t>●OUTPUT</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -65,9 +77,6 @@
     <t>IDでユーザーを取得する。</t>
   </si>
   <si>
-    <t>INPUT</t>
-  </si>
-  <si>
     <t>ユーザーID</t>
   </si>
   <si>
@@ -75,9 +84,6 @@
   </si>
   <si>
     <t>Long</t>
-  </si>
-  <si>
-    <t>OUTPUT</t>
   </si>
   <si>
     <t>ユーザーエンティティ。</t>
@@ -834,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -850,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -872,14 +878,12 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -888,14 +892,12 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -905,548 +907,548 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" t="s" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
+      <c r="A16" t="s" s="3">
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>12</v>
+      <c r="A17" t="s" s="3">
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1.0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E21" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="H21" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="true">
       <c r="A27" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="true">
       <c r="A28" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" ht="15.0" customHeight="true">
       <c r="A29" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" ht="15.0" customHeight="true">
       <c r="A30" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="true">
       <c r="A31" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" ht="15.0" customHeight="true">
       <c r="A32" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" ht="15.0" customHeight="true">
       <c r="A33" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="true">
@@ -1463,11 +1465,9 @@
       <c r="A35" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B35" s="28"/>
       <c r="C35" s="29" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D35" s="30"/>
       <c r="E35" s="31"/>
@@ -1477,13 +1477,11 @@
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B36" s="36"/>
       <c r="C36" s="37" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D36" s="38"/>
       <c r="E36" s="39"/>
@@ -1493,964 +1491,964 @@
     </row>
     <row r="37" ht="15.0" customHeight="true">
       <c r="A37" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B37" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F37" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" ht="15.0" customHeight="true">
       <c r="A38" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B38" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E38" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F38" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G38" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H38" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="true">
       <c r="A39" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" ht="15.0" customHeight="true">
       <c r="A41" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="true">
       <c r="A42" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" ht="15.0" customHeight="true">
       <c r="A43" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E43" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="H43" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="true">
       <c r="A44" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="true">
       <c r="A45" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" ht="15.0" customHeight="true">
       <c r="A46" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" ht="15.0" customHeight="true">
       <c r="A47" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="true">
       <c r="A48" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" ht="15.0" customHeight="true">
       <c r="A49" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" ht="15.0" customHeight="true">
       <c r="A50" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B50" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="true">
       <c r="A51" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B51" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" ht="15.0" customHeight="true">
       <c r="A52" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B52" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" ht="15.0" customHeight="true">
       <c r="A53" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="true">
       <c r="A54" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B54" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" ht="15.0" customHeight="true">
       <c r="A55" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B55" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" ht="15.0" customHeight="true">
       <c r="A56" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B56" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C56" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D56" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E56" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F56" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G56" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H56" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="true">
       <c r="A57" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B57" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" ht="15.0" customHeight="true">
       <c r="A58" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B58" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" ht="15.0" customHeight="true">
       <c r="A59" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B59" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" ht="15.0" customHeight="true">
       <c r="A60" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B60" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" ht="15.0" customHeight="true">
       <c r="A61" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B61" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E61" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F61" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="H61" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" ht="15.0" customHeight="true">
       <c r="A62" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B62" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="true">
       <c r="A63" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B63" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" ht="15.0" customHeight="true">
       <c r="A64" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B64" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" ht="15.0" customHeight="true">
       <c r="A65" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B65" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="true">
       <c r="A66" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B66" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" ht="15.0" customHeight="true">
       <c r="A67" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B67" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" ht="15.0" customHeight="true">
       <c r="A68" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B68" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="true">
       <c r="A69" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B69" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" ht="15.0" customHeight="true">
       <c r="A70" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B70" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" ht="15.0" customHeight="true">
       <c r="A71" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B71" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="true">
       <c r="A72" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B72" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" ht="15.0" customHeight="true">
       <c r="A73" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B73" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" ht="15.0" customHeight="true">
@@ -2467,11 +2465,9 @@
       <c r="A75" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B75" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B75" s="28"/>
       <c r="C75" s="29" t="s">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="D75" s="30"/>
       <c r="E75" s="31"/>
@@ -2481,13 +2477,11 @@
     </row>
     <row r="76" ht="15.0" customHeight="true">
       <c r="A76" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B76" s="36"/>
       <c r="C76" s="37" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D76" s="38"/>
       <c r="E76" s="39"/>
@@ -2497,756 +2491,756 @@
     </row>
     <row r="77" ht="15.0" customHeight="true">
       <c r="A77" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B77" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C77" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D77" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F77" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G77" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H77" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" ht="15.0" customHeight="true">
       <c r="A78" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B78" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C78" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D78" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E78" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F78" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G78" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H78" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" ht="15.0" customHeight="true">
       <c r="A79" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B79" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" ht="15.0" customHeight="true">
       <c r="A80" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B80" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" ht="15.0" customHeight="true">
       <c r="A81" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B81" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E81" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F81" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G81" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="H81" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" ht="15.0" customHeight="true">
       <c r="A82" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B82" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" ht="15.0" customHeight="true">
       <c r="A83" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B83" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" ht="15.0" customHeight="true">
       <c r="A84" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B84" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" ht="15.0" customHeight="true">
       <c r="A85" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B85" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" ht="15.0" customHeight="true">
       <c r="A86" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B86" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" ht="15.0" customHeight="true">
       <c r="A87" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B87" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" ht="15.0" customHeight="true">
       <c r="A88" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B88" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E88" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F88" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F88" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G88" s="17" t="s">
-        <v>83</v>
-      </c>
       <c r="H88" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" ht="15.0" customHeight="true">
       <c r="A89" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B89" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" ht="15.0" customHeight="true">
       <c r="A90" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B90" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G90" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" ht="15.0" customHeight="true">
       <c r="A91" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B91" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" ht="15.0" customHeight="true">
       <c r="A92" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B92" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" ht="15.0" customHeight="true">
       <c r="A93" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B93" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E93" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F93" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F93" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" s="17" t="s">
-        <v>83</v>
-      </c>
       <c r="H93" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" ht="15.0" customHeight="true">
       <c r="A94" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B94" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" ht="15.0" customHeight="true">
       <c r="A95" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B95" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" ht="15.0" customHeight="true">
       <c r="A96" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B96" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C96" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D96" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E96" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F96" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G96" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H96" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" ht="15.0" customHeight="true">
       <c r="A97" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B97" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" ht="15.0" customHeight="true">
       <c r="A98" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B98" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" ht="15.0" customHeight="true">
       <c r="A99" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B99" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" ht="15.0" customHeight="true">
       <c r="A100" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B100" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" ht="15.0" customHeight="true">
       <c r="A101" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B101" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" ht="15.0" customHeight="true">
       <c r="A102" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B102" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G102" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" ht="15.0" customHeight="true">
       <c r="A103" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B103" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G103" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" ht="15.0" customHeight="true">
       <c r="A104" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B104" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" ht="15.0" customHeight="true">
       <c r="A105" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B105" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" ht="15.0" customHeight="true">
@@ -3263,11 +3257,9 @@
       <c r="A107" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B107" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B107" s="28"/>
       <c r="C107" s="29" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="D107" s="30"/>
       <c r="E107" s="31"/>
@@ -3277,13 +3269,11 @@
     </row>
     <row r="108" ht="15.0" customHeight="true">
       <c r="A108" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B108" s="36"/>
       <c r="C108" s="37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D108" s="38"/>
       <c r="E108" s="39"/>
@@ -3293,548 +3283,548 @@
     </row>
     <row r="109" ht="15.0" customHeight="true">
       <c r="A109" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B109" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C109" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D109" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E109" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F109" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G109" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H109" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" ht="15.0" customHeight="true">
       <c r="A110" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B110" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C110" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D110" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E110" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F110" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G110" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H110" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" ht="15.0" customHeight="true">
       <c r="A111" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B111" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H111" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" ht="15.0" customHeight="true">
       <c r="A112" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B112" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C112" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D112" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E112" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F112" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G112" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H112" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" ht="15.0" customHeight="true">
       <c r="A113" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B113" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F113" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H113" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" ht="15.0" customHeight="true">
       <c r="A114" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B114" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" ht="15.0" customHeight="true">
       <c r="A115" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B115" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F115" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" ht="15.0" customHeight="true">
       <c r="A116" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B116" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F116" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" ht="15.0" customHeight="true">
       <c r="A117" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B117" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E117" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F117" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F117" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G117" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="H117" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" ht="15.0" customHeight="true">
       <c r="A118" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B118" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F118" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H118" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" ht="15.0" customHeight="true">
       <c r="A119" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B119" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F119" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" ht="15.0" customHeight="true">
       <c r="A120" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B120" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F120" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" ht="15.0" customHeight="true">
       <c r="A121" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B121" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F121" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H121" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" ht="15.0" customHeight="true">
       <c r="A122" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B122" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H122" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" ht="15.0" customHeight="true">
       <c r="A123" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B123" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F123" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H123" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" ht="15.0" customHeight="true">
       <c r="A124" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B124" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H124" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" ht="15.0" customHeight="true">
       <c r="A125" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B125" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" ht="15.0" customHeight="true">
       <c r="A126" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B126" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" ht="15.0" customHeight="true">
       <c r="A127" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B127" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H127" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" ht="15.0" customHeight="true">
       <c r="A128" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B128" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H128" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" ht="15.0" customHeight="true">
       <c r="A129" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B129" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H129" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" ht="15.0" customHeight="true">
@@ -3851,11 +3841,9 @@
       <c r="A131" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B131" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B131" s="28"/>
       <c r="C131" s="29" t="s">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="D131" s="30"/>
       <c r="E131" s="31"/>
@@ -3865,13 +3853,11 @@
     </row>
     <row r="132" ht="15.0" customHeight="true">
       <c r="A132" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B132" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B132" s="36"/>
       <c r="C132" s="37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D132" s="38"/>
       <c r="E132" s="39"/>
@@ -3881,132 +3867,132 @@
     </row>
     <row r="133" ht="15.0" customHeight="true">
       <c r="A133" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B133" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C133" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D133" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E133" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F133" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G133" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H133" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" ht="15.0" customHeight="true">
       <c r="A134" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B134" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C134" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D134" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E134" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F134" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G134" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H134" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" ht="15.0" customHeight="true">
       <c r="A135" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B135" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B135" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H135" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" ht="15.0" customHeight="true">
       <c r="A136" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B136" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C136" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D136" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E136" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F136" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G136" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H136" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" ht="15.0" customHeight="true">
       <c r="A137" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F137" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H137" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" ht="15.0" customHeight="true">
@@ -4023,11 +4009,9 @@
       <c r="A139" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B139" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B139" s="28"/>
       <c r="C139" s="29" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="D139" s="30"/>
       <c r="E139" s="31"/>
@@ -4037,13 +4021,11 @@
     </row>
     <row r="140" ht="15.0" customHeight="true">
       <c r="A140" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B140" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="B140" s="36"/>
       <c r="C140" s="37" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D140" s="38"/>
       <c r="E140" s="39"/>
@@ -4053,106 +4035,106 @@
     </row>
     <row r="141" ht="15.0" customHeight="true">
       <c r="A141" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B141" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C141" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D141" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E141" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F141" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G141" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H141" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" ht="15.0" customHeight="true">
       <c r="A142" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B142" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C142" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D142" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E142" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F142" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G142" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H142" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" ht="15.0" customHeight="true">
       <c r="A143" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B143" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B143" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H143" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" ht="15.0" customHeight="true">
       <c r="A144" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B144" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B144" s="12" t="n">
+        <v>2.0</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F144" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H144" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" ht="15.0" customHeight="true">
@@ -4169,11 +4151,9 @@
       <c r="A146" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B146" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B146" s="28"/>
       <c r="C146" s="29" t="s">
-        <v>126</v>
+        <v>3</v>
       </c>
       <c r="D146" s="30"/>
       <c r="E146" s="31"/>
@@ -4183,13 +4163,11 @@
     </row>
     <row r="147" ht="15.0" customHeight="true">
       <c r="A147" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B147" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B147" s="36"/>
       <c r="C147" s="37" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D147" s="38"/>
       <c r="E147" s="39"/>
@@ -4199,132 +4177,132 @@
     </row>
     <row r="148" ht="15.0" customHeight="true">
       <c r="A148" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B148" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C148" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D148" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E148" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F148" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G148" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H148" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" ht="15.0" customHeight="true">
       <c r="A149" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B149" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C149" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D149" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E149" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F149" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G149" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H149" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" ht="15.0" customHeight="true">
       <c r="A150" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B150" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B150" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F150" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H150" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" ht="15.0" customHeight="true">
       <c r="A151" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B151" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C151" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D151" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E151" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F151" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G151" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H151" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="152" ht="15.0" customHeight="true">
       <c r="A152" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" ht="15.0" customHeight="true">
@@ -4341,11 +4319,9 @@
       <c r="A154" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B154" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B154" s="28"/>
       <c r="C154" s="29" t="s">
-        <v>131</v>
+        <v>3</v>
       </c>
       <c r="D154" s="30"/>
       <c r="E154" s="31"/>
@@ -4355,13 +4331,11 @@
     </row>
     <row r="155" ht="15.0" customHeight="true">
       <c r="A155" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B155" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B155" s="36"/>
       <c r="C155" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D155" s="38"/>
       <c r="E155" s="39"/>
@@ -4371,132 +4345,132 @@
     </row>
     <row r="156" ht="15.0" customHeight="true">
       <c r="A156" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B156" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C156" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D156" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E156" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F156" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G156" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H156" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" ht="15.0" customHeight="true">
       <c r="A157" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B157" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C157" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D157" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E157" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F157" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G157" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H157" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" ht="15.0" customHeight="true">
       <c r="A158" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B158" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B158" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F158" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H158" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" ht="15.0" customHeight="true">
       <c r="A159" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B159" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C159" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D159" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E159" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F159" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G159" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H159" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" ht="15.0" customHeight="true">
       <c r="A160" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H160" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" ht="15.0" customHeight="true">
@@ -4513,11 +4487,9 @@
       <c r="A162" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B162" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B162" s="28"/>
       <c r="C162" s="29" t="s">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="D162" s="30"/>
       <c r="E162" s="31"/>
@@ -4527,13 +4499,11 @@
     </row>
     <row r="163" ht="15.0" customHeight="true">
       <c r="A163" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B163" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B163" s="36"/>
       <c r="C163" s="37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D163" s="38"/>
       <c r="E163" s="39"/>
@@ -4543,574 +4513,574 @@
     </row>
     <row r="164" ht="15.0" customHeight="true">
       <c r="A164" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B164" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C164" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D164" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E164" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F164" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G164" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H164" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" ht="15.0" customHeight="true">
       <c r="A165" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B165" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C165" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D165" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E165" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F165" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G165" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H165" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166" ht="15.0" customHeight="true">
       <c r="A166" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B166" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B166" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C166" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D166" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F166" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H166" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" ht="15.0" customHeight="true">
       <c r="A167" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B167" s="12" t="n">
+        <v>2.0</v>
       </c>
       <c r="C167" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F167" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H167" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" ht="15.0" customHeight="true">
       <c r="A168" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B168" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C168" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D168" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E168" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F168" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G168" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H168" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" ht="15.0" customHeight="true">
       <c r="A169" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B169" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C169" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F169" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G169" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H169" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" ht="15.0" customHeight="true">
       <c r="A170" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B170" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F170" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G170" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H170" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" ht="15.0" customHeight="true">
       <c r="A171" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B171" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C171" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E171" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F171" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G171" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" ht="15.0" customHeight="true">
       <c r="A172" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B172" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F172" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G172" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H172" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" ht="15.0" customHeight="true">
       <c r="A173" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B173" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C173" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E173" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F173" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G173" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F173" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G173" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="H173" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" ht="15.0" customHeight="true">
       <c r="A174" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B174" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F174" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G174" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H174" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" ht="15.0" customHeight="true">
       <c r="A175" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B175" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F175" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G175" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H175" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" ht="15.0" customHeight="true">
       <c r="A176" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B176" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C176" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F176" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" ht="15.0" customHeight="true">
       <c r="A177" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B177" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C177" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F177" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G177" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H177" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" ht="15.0" customHeight="true">
       <c r="A178" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B178" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C178" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F178" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G178" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H178" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" ht="15.0" customHeight="true">
       <c r="A179" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B179" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C179" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E179" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F179" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G179" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H179" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="180" ht="15.0" customHeight="true">
       <c r="A180" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B180" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C180" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E180" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F180" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H180" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" ht="15.0" customHeight="true">
       <c r="A181" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B181" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C181" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E181" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F181" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H181" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" ht="15.0" customHeight="true">
       <c r="A182" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B182" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C182" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E182" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F182" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G182" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H182" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" ht="15.0" customHeight="true">
       <c r="A183" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B183" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C183" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E183" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F183" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G183" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H183" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" ht="15.0" customHeight="true">
       <c r="A184" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B184" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C184" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F184" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G184" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H184" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" ht="15.0" customHeight="true">
       <c r="A185" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B185" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C185" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F185" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G185" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H185" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" ht="15.0" customHeight="true">
@@ -5125,13 +5095,13 @@
     </row>
     <row r="187" ht="15.0" customHeight="true">
       <c r="A187" s="67" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B187" s="68" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C187" s="69" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D187" s="70"/>
       <c r="E187" s="71"/>
@@ -5140,66 +5110,104 @@
       <c r="H187" s="74"/>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="s">
-        <v>141</v>
+      <c r="A188" s="10" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="s">
-        <v>142</v>
+      <c r="A189" s="10" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="s">
-        <v>143</v>
+      <c r="A190" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="s">
-        <v>144</v>
+      <c r="A191" s="10" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="s">
-        <v>12</v>
+      <c r="A192" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="s">
-        <v>145</v>
+      <c r="A193" s="10" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="s">
-        <v>146</v>
+      <c r="A194" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="s">
-        <v>147</v>
+      <c r="A195" s="10" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="s">
-        <v>148</v>
+      <c r="A196" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="s">
-        <v>149</v>
+      <c r="A197" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="s">
-        <v>12</v>
+      <c r="A198" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="s">
-        <v>150</v>
+      <c r="A199" s="10" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:H75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="C107:H107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:H108"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="C132:H132"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="A146:B146"/>
+    <mergeCell ref="C146:H146"/>
+    <mergeCell ref="A147:B147"/>
+    <mergeCell ref="C147:H147"/>
+    <mergeCell ref="A154:B154"/>
+    <mergeCell ref="C154:H154"/>
+    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="C155:H155"/>
+    <mergeCell ref="A162:B162"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="C163:H163"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/output/UserRepository.xlsx
+++ b/output/UserRepository.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="213">
   <si>
     <t xml:space="preserve">Repository</t>
   </si>
@@ -247,15 +247,12 @@
     <t>ユーザーエンティティ。</t>
   </si>
   <si>
-    <t>USER</t>
+    <t>-</t>
   </si>
   <si>
     <t>User</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">  ユーザーID</t>
   </si>
   <si>
@@ -388,7 +385,7 @@
     <t xml:space="preserve">  監査情報</t>
   </si>
   <si>
-    <t xml:space="preserve">  AUDIT_INFO</t>
+    <t xml:space="preserve">  -</t>
   </si>
   <si>
     <t xml:space="preserve">  auditInfo</t>
@@ -454,9 +451,6 @@
     <t>検索条件</t>
   </si>
   <si>
-    <t>CONDITION</t>
-  </si>
-  <si>
     <t>condition</t>
   </si>
   <si>
@@ -538,9 +532,6 @@
     <t>ページング要求</t>
   </si>
   <si>
-    <t>PAGE_REQUEST</t>
-  </si>
-  <si>
     <t>pageRequest</t>
   </si>
   <si>
@@ -559,9 +550,6 @@
     <t>ページング結果を表す共通DTO。</t>
   </si>
   <si>
-    <t>PAGE_RESULT</t>
-  </si>
-  <si>
     <t>PageResult</t>
   </si>
   <si>
@@ -571,9 +559,6 @@
     <t xml:space="preserve">  取得結果</t>
   </si>
   <si>
-    <t xml:space="preserve">  CONTENT</t>
-  </si>
-  <si>
     <t xml:space="preserve">  content</t>
   </si>
   <si>
@@ -599,9 +584,6 @@
   </si>
   <si>
     <t xml:space="preserve">  ページング要求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PAGE_REQUEST</t>
   </si>
   <si>
     <t xml:space="preserve">  pageRequest</t>
@@ -1672,7 +1654,7 @@
         <v>42</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>42</v>
@@ -1689,13 +1671,13 @@
         <v>2.0</v>
       </c>
       <c r="C18" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>37</v>
@@ -1715,19 +1697,19 @@
         <v>3.0</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="E19" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="F19" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H19" s="22" t="s">
         <v>17</v>
@@ -1741,19 +1723,19 @@
         <v>4.0</v>
       </c>
       <c r="C20" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="F20" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="G20" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H20" s="22" t="s">
         <v>17</v>
@@ -1767,19 +1749,19 @@
         <v>5.0</v>
       </c>
       <c r="C21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="E21" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>58</v>
-      </c>
       <c r="F21" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H21" s="22" t="s">
         <v>17</v>
@@ -1793,19 +1775,19 @@
         <v>6.0</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="19" t="s">
-        <v>61</v>
-      </c>
       <c r="F22" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H22" s="22" t="s">
         <v>17</v>
@@ -1819,19 +1801,19 @@
         <v>7.0</v>
       </c>
       <c r="C23" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="E23" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>64</v>
-      </c>
       <c r="F23" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H23" s="22" t="s">
         <v>17</v>
@@ -1845,19 +1827,19 @@
         <v>8.0</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="E24" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="F24" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="G24" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H24" s="22" t="s">
         <v>17</v>
@@ -1871,19 +1853,19 @@
         <v>9.0</v>
       </c>
       <c r="C25" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="F25" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>17</v>
@@ -1897,19 +1879,19 @@
         <v>10.0</v>
       </c>
       <c r="C26" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="E26" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="F26" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H26" s="22" t="s">
         <v>17</v>
@@ -1923,19 +1905,19 @@
         <v>11.0</v>
       </c>
       <c r="C27" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="E27" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="F27" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H27" s="22" t="s">
         <v>17</v>
@@ -1949,19 +1931,19 @@
         <v>12.0</v>
       </c>
       <c r="C28" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="E28" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="F28" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="G28" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="H28" s="22" t="s">
         <v>17</v>
@@ -1975,19 +1957,19 @@
         <v>13.0</v>
       </c>
       <c r="C29" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="E29" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="F29" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>90</v>
       </c>
       <c r="H29" s="22" t="s">
         <v>17</v>
@@ -2001,19 +1983,19 @@
         <v>14.0</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="E30" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="19" t="s">
-        <v>93</v>
-      </c>
       <c r="F30" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H30" s="22" t="s">
         <v>17</v>
@@ -2027,19 +2009,19 @@
         <v>15.0</v>
       </c>
       <c r="C31" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="E31" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="F31" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H31" s="22" t="s">
         <v>17</v>
@@ -2053,19 +2035,19 @@
         <v>16.0</v>
       </c>
       <c r="C32" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E32" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="F32" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H32" s="22" t="s">
         <v>17</v>
@@ -2079,19 +2061,19 @@
         <v>17.0</v>
       </c>
       <c r="C33" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="E33" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="19" t="s">
-        <v>102</v>
-      </c>
       <c r="F33" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H33" s="22" t="s">
         <v>17</v>
@@ -2123,11 +2105,11 @@
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B36" s="40"/>
       <c r="C36" s="41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
@@ -2195,16 +2177,16 @@
         <v>1.0</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>41</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G39" s="21" t="s">
         <v>42</v>
@@ -2221,13 +2203,13 @@
         <v>2.0</v>
       </c>
       <c r="C40" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="E40" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>37</v>
@@ -2247,19 +2229,19 @@
         <v>3.0</v>
       </c>
       <c r="C41" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="E41" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="F41" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G41" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H41" s="22" t="s">
         <v>17</v>
@@ -2273,19 +2255,19 @@
         <v>4.0</v>
       </c>
       <c r="C42" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="E42" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="F42" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="G42" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G42" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H42" s="22" t="s">
         <v>17</v>
@@ -2299,19 +2281,19 @@
         <v>5.0</v>
       </c>
       <c r="C43" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="E43" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E43" s="19" t="s">
-        <v>58</v>
-      </c>
       <c r="F43" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G43" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H43" s="22" t="s">
         <v>17</v>
@@ -2325,19 +2307,19 @@
         <v>6.0</v>
       </c>
       <c r="C44" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="E44" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="19" t="s">
-        <v>61</v>
-      </c>
       <c r="F44" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G44" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H44" s="22" t="s">
         <v>17</v>
@@ -2351,19 +2333,19 @@
         <v>7.0</v>
       </c>
       <c r="C45" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="E45" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="19" t="s">
-        <v>64</v>
-      </c>
       <c r="F45" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H45" s="22" t="s">
         <v>17</v>
@@ -2377,19 +2359,19 @@
         <v>8.0</v>
       </c>
       <c r="C46" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="E46" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="F46" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="G46" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G46" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H46" s="22" t="s">
         <v>17</v>
@@ -2403,19 +2385,19 @@
         <v>9.0</v>
       </c>
       <c r="C47" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="E47" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="F47" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G47" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="H47" s="22" t="s">
         <v>17</v>
@@ -2429,19 +2411,19 @@
         <v>10.0</v>
       </c>
       <c r="C48" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="E48" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="F48" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G48" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H48" s="22" t="s">
         <v>17</v>
@@ -2455,19 +2437,19 @@
         <v>11.0</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="E49" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="F49" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G49" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H49" s="22" t="s">
         <v>17</v>
@@ -2481,19 +2463,19 @@
         <v>12.0</v>
       </c>
       <c r="C50" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="E50" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="F50" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="G50" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="H50" s="22" t="s">
         <v>17</v>
@@ -2507,19 +2489,19 @@
         <v>13.0</v>
       </c>
       <c r="C51" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="F51" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>90</v>
       </c>
       <c r="H51" s="22" t="s">
         <v>17</v>
@@ -2533,19 +2515,19 @@
         <v>14.0</v>
       </c>
       <c r="C52" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="E52" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E52" s="19" t="s">
-        <v>93</v>
-      </c>
       <c r="F52" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G52" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H52" s="22" t="s">
         <v>17</v>
@@ -2559,19 +2541,19 @@
         <v>15.0</v>
       </c>
       <c r="C53" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="E53" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E53" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="F53" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H53" s="22" t="s">
         <v>17</v>
@@ -2585,19 +2567,19 @@
         <v>16.0</v>
       </c>
       <c r="C54" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="E54" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E54" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="F54" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G54" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H54" s="22" t="s">
         <v>17</v>
@@ -2611,19 +2593,19 @@
         <v>17.0</v>
       </c>
       <c r="C55" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="E55" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E55" s="19" t="s">
-        <v>102</v>
-      </c>
       <c r="F55" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H55" s="22" t="s">
         <v>17</v>
@@ -2672,7 +2654,7 @@
         <v>42</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G57" s="21" t="s">
         <v>42</v>
@@ -2689,13 +2671,13 @@
         <v>2.0</v>
       </c>
       <c r="C58" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="E58" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F58" s="20" t="s">
         <v>37</v>
@@ -2715,19 +2697,19 @@
         <v>3.0</v>
       </c>
       <c r="C59" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="E59" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="F59" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="F59" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G59" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H59" s="22" t="s">
         <v>17</v>
@@ -2741,19 +2723,19 @@
         <v>4.0</v>
       </c>
       <c r="C60" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="E60" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="F60" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="G60" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G60" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H60" s="22" t="s">
         <v>17</v>
@@ -2767,19 +2749,19 @@
         <v>5.0</v>
       </c>
       <c r="C61" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="E61" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E61" s="19" t="s">
-        <v>58</v>
-      </c>
       <c r="F61" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G61" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H61" s="22" t="s">
         <v>17</v>
@@ -2793,19 +2775,19 @@
         <v>6.0</v>
       </c>
       <c r="C62" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="E62" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E62" s="19" t="s">
-        <v>61</v>
-      </c>
       <c r="F62" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H62" s="22" t="s">
         <v>17</v>
@@ -2819,19 +2801,19 @@
         <v>7.0</v>
       </c>
       <c r="C63" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="E63" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E63" s="19" t="s">
-        <v>64</v>
-      </c>
       <c r="F63" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G63" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G63" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H63" s="22" t="s">
         <v>17</v>
@@ -2845,19 +2827,19 @@
         <v>8.0</v>
       </c>
       <c r="C64" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="E64" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="F64" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="G64" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G64" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H64" s="22" t="s">
         <v>17</v>
@@ -2871,19 +2853,19 @@
         <v>9.0</v>
       </c>
       <c r="C65" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="E65" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="F65" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G65" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="F65" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G65" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="H65" s="22" t="s">
         <v>17</v>
@@ -2897,19 +2879,19 @@
         <v>10.0</v>
       </c>
       <c r="C66" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="E66" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="F66" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G66" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G66" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H66" s="22" t="s">
         <v>17</v>
@@ -2923,19 +2905,19 @@
         <v>11.0</v>
       </c>
       <c r="C67" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="E67" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E67" s="19" t="s">
+      <c r="F67" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G67" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F67" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G67" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H67" s="22" t="s">
         <v>17</v>
@@ -2949,19 +2931,19 @@
         <v>12.0</v>
       </c>
       <c r="C68" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="E68" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E68" s="19" t="s">
+      <c r="F68" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="G68" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="G68" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="H68" s="22" t="s">
         <v>17</v>
@@ -2975,19 +2957,19 @@
         <v>13.0</v>
       </c>
       <c r="C69" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="E69" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="F69" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G69" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="F69" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G69" s="21" t="s">
-        <v>90</v>
       </c>
       <c r="H69" s="22" t="s">
         <v>17</v>
@@ -3001,19 +2983,19 @@
         <v>14.0</v>
       </c>
       <c r="C70" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D70" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="E70" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>93</v>
-      </c>
       <c r="F70" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G70" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G70" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H70" s="22" t="s">
         <v>17</v>
@@ -3027,19 +3009,19 @@
         <v>15.0</v>
       </c>
       <c r="C71" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D71" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="E71" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E71" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="F71" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G71" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H71" s="22" t="s">
         <v>17</v>
@@ -3053,19 +3035,19 @@
         <v>16.0</v>
       </c>
       <c r="C72" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="18" t="s">
+      <c r="E72" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E72" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="F72" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G72" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G72" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H72" s="22" t="s">
         <v>17</v>
@@ -3079,19 +3061,19 @@
         <v>17.0</v>
       </c>
       <c r="C73" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="E73" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E73" s="19" t="s">
-        <v>102</v>
-      </c>
       <c r="F73" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G73" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H73" s="22" t="s">
         <v>17</v>
@@ -3123,11 +3105,11 @@
     </row>
     <row r="76" ht="15.0" customHeight="true">
       <c r="A76" s="39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" s="40"/>
       <c r="C76" s="41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D76" s="42"/>
       <c r="E76" s="43"/>
@@ -3195,19 +3177,19 @@
         <v>1.0</v>
       </c>
       <c r="C79" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="F79" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79" s="21" t="s">
         <v>110</v>
-      </c>
-      <c r="E79" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="F79" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>112</v>
       </c>
       <c r="H79" s="22" t="s">
         <v>17</v>
@@ -3221,19 +3203,19 @@
         <v>2.0</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D80" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E80" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E80" s="19" t="s">
+      <c r="F80" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F80" s="20" t="s">
+      <c r="G80" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G80" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H80" s="22" t="s">
         <v>17</v>
@@ -3247,19 +3229,19 @@
         <v>3.0</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D81" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E81" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E81" s="19" t="s">
-        <v>58</v>
-      </c>
       <c r="F81" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G81" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G81" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H81" s="22" t="s">
         <v>17</v>
@@ -3273,19 +3255,19 @@
         <v>4.0</v>
       </c>
       <c r="C82" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D82" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D82" s="18" t="s">
+      <c r="E82" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E82" s="19" t="s">
-        <v>61</v>
-      </c>
       <c r="F82" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G82" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G82" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H82" s="22" t="s">
         <v>17</v>
@@ -3299,19 +3281,19 @@
         <v>5.0</v>
       </c>
       <c r="C83" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D83" s="18" t="s">
+      <c r="E83" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E83" s="19" t="s">
+      <c r="F83" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G83" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="F83" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G83" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H83" s="22" t="s">
         <v>17</v>
@@ -3325,19 +3307,19 @@
         <v>6.0</v>
       </c>
       <c r="C84" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E84" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D84" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>117</v>
-      </c>
       <c r="F84" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G84" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G84" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H84" s="22" t="s">
         <v>17</v>
@@ -3351,19 +3333,19 @@
         <v>7.0</v>
       </c>
       <c r="C85" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E85" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D85" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>120</v>
-      </c>
       <c r="F85" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G85" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G85" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H85" s="22" t="s">
         <v>17</v>
@@ -3377,19 +3359,19 @@
         <v>8.0</v>
       </c>
       <c r="C86" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D86" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E86" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D86" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>123</v>
-      </c>
       <c r="F86" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G86" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H86" s="22" t="s">
         <v>17</v>
@@ -3403,19 +3385,19 @@
         <v>9.0</v>
       </c>
       <c r="C87" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E87" s="19" t="s">
         <v>124</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>126</v>
       </c>
       <c r="F87" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G87" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H87" s="22" t="s">
         <v>17</v>
@@ -3429,19 +3411,19 @@
         <v>10.0</v>
       </c>
       <c r="C88" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D88" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E88" s="19" t="s">
         <v>128</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>130</v>
       </c>
       <c r="F88" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G88" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H88" s="22" t="s">
         <v>17</v>
@@ -3455,19 +3437,19 @@
         <v>11.0</v>
       </c>
       <c r="C89" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E89" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D89" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E89" s="19" t="s">
-        <v>133</v>
-      </c>
       <c r="F89" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G89" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G89" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H89" s="22" t="s">
         <v>17</v>
@@ -3481,19 +3463,19 @@
         <v>12.0</v>
       </c>
       <c r="C90" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E90" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D90" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>136</v>
-      </c>
       <c r="F90" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G90" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="G90" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="H90" s="22" t="s">
         <v>17</v>
@@ -3507,19 +3489,19 @@
         <v>13.0</v>
       </c>
       <c r="C91" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G91" s="21" t="s">
         <v>137</v>
-      </c>
-      <c r="D91" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="F91" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G91" s="21" t="s">
-        <v>140</v>
       </c>
       <c r="H91" s="22" t="s">
         <v>17</v>
@@ -3533,19 +3515,19 @@
         <v>14.0</v>
       </c>
       <c r="C92" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E92" s="19" t="s">
         <v>124</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E92" s="19" t="s">
-        <v>126</v>
       </c>
       <c r="F92" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G92" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H92" s="22" t="s">
         <v>17</v>
@@ -3559,19 +3541,19 @@
         <v>15.0</v>
       </c>
       <c r="C93" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E93" s="19" t="s">
         <v>128</v>
-      </c>
-      <c r="D93" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E93" s="19" t="s">
-        <v>130</v>
       </c>
       <c r="F93" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G93" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H93" s="22" t="s">
         <v>17</v>
@@ -3585,19 +3567,19 @@
         <v>16.0</v>
       </c>
       <c r="C94" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E94" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D94" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>133</v>
-      </c>
       <c r="F94" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G94" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G94" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H94" s="22" t="s">
         <v>17</v>
@@ -3611,19 +3593,19 @@
         <v>17.0</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D95" s="18" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F95" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G95" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G95" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H95" s="22" t="s">
         <v>17</v>
@@ -3663,19 +3645,19 @@
         <v>1.0</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G97" s="21" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H97" s="22" t="s">
         <v>17</v>
@@ -3689,19 +3671,19 @@
         <v>2.0</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G98" s="21" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H98" s="22" t="s">
         <v>17</v>
@@ -3715,13 +3697,13 @@
         <v>3.0</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D99" s="18" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F99" s="20" t="s">
         <v>37</v>
@@ -3741,19 +3723,19 @@
         <v>4.0</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F100" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H100" s="22" t="s">
         <v>17</v>
@@ -3767,19 +3749,19 @@
         <v>5.0</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H101" s="22" t="s">
         <v>17</v>
@@ -3793,19 +3775,19 @@
         <v>6.0</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F102" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G102" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H102" s="22" t="s">
         <v>17</v>
@@ -3819,19 +3801,19 @@
         <v>7.0</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F103" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G103" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H103" s="22" t="s">
         <v>17</v>
@@ -3845,19 +3827,19 @@
         <v>8.0</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D104" s="18" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F104" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G104" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G104" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H104" s="22" t="s">
         <v>17</v>
@@ -3871,19 +3853,19 @@
         <v>9.0</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F105" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G105" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G105" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H105" s="22" t="s">
         <v>17</v>
@@ -3915,11 +3897,11 @@
     </row>
     <row r="108" ht="15.0" customHeight="true">
       <c r="A108" s="39" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B108" s="40"/>
       <c r="C108" s="41" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D108" s="42"/>
       <c r="E108" s="43"/>
@@ -3987,19 +3969,19 @@
         <v>1.0</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D111" s="18" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F111" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G111" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G111" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H111" s="22" t="s">
         <v>17</v>
@@ -4048,10 +4030,10 @@
         <v>42</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G113" s="21" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H113" s="22" t="s">
         <v>17</v>
@@ -4065,13 +4047,13 @@
         <v>2.0</v>
       </c>
       <c r="C114" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D114" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D114" s="18" t="s">
+      <c r="E114" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E114" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F114" s="20" t="s">
         <v>37</v>
@@ -4091,19 +4073,19 @@
         <v>3.0</v>
       </c>
       <c r="C115" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D115" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D115" s="18" t="s">
+      <c r="E115" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E115" s="19" t="s">
+      <c r="F115" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G115" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="F115" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G115" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H115" s="22" t="s">
         <v>17</v>
@@ -4117,19 +4099,19 @@
         <v>4.0</v>
       </c>
       <c r="C116" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D116" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D116" s="18" t="s">
+      <c r="E116" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E116" s="19" t="s">
+      <c r="F116" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F116" s="20" t="s">
+      <c r="G116" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G116" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H116" s="22" t="s">
         <v>17</v>
@@ -4143,19 +4125,19 @@
         <v>5.0</v>
       </c>
       <c r="C117" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D117" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D117" s="18" t="s">
+      <c r="E117" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E117" s="19" t="s">
-        <v>58</v>
-      </c>
       <c r="F117" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G117" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G117" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H117" s="22" t="s">
         <v>17</v>
@@ -4169,19 +4151,19 @@
         <v>6.0</v>
       </c>
       <c r="C118" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D118" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D118" s="18" t="s">
+      <c r="E118" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E118" s="19" t="s">
-        <v>61</v>
-      </c>
       <c r="F118" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G118" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G118" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H118" s="22" t="s">
         <v>17</v>
@@ -4195,19 +4177,19 @@
         <v>7.0</v>
       </c>
       <c r="C119" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D119" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D119" s="18" t="s">
+      <c r="E119" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E119" s="19" t="s">
-        <v>64</v>
-      </c>
       <c r="F119" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G119" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G119" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H119" s="22" t="s">
         <v>17</v>
@@ -4221,19 +4203,19 @@
         <v>8.0</v>
       </c>
       <c r="C120" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D120" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D120" s="18" t="s">
+      <c r="E120" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E120" s="19" t="s">
+      <c r="F120" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F120" s="20" t="s">
+      <c r="G120" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G120" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H120" s="22" t="s">
         <v>17</v>
@@ -4247,19 +4229,19 @@
         <v>9.0</v>
       </c>
       <c r="C121" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D121" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D121" s="18" t="s">
+      <c r="E121" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E121" s="19" t="s">
+      <c r="F121" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G121" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="F121" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G121" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="H121" s="22" t="s">
         <v>17</v>
@@ -4273,19 +4255,19 @@
         <v>10.0</v>
       </c>
       <c r="C122" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D122" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D122" s="18" t="s">
+      <c r="E122" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E122" s="19" t="s">
+      <c r="F122" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G122" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="F122" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G122" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H122" s="22" t="s">
         <v>17</v>
@@ -4299,19 +4281,19 @@
         <v>11.0</v>
       </c>
       <c r="C123" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D123" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D123" s="18" t="s">
+      <c r="E123" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E123" s="19" t="s">
+      <c r="F123" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G123" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F123" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G123" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H123" s="22" t="s">
         <v>17</v>
@@ -4325,19 +4307,19 @@
         <v>12.0</v>
       </c>
       <c r="C124" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D124" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D124" s="18" t="s">
+      <c r="E124" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E124" s="19" t="s">
+      <c r="F124" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F124" s="20" t="s">
+      <c r="G124" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="G124" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="H124" s="22" t="s">
         <v>17</v>
@@ -4351,19 +4333,19 @@
         <v>13.0</v>
       </c>
       <c r="C125" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D125" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D125" s="18" t="s">
+      <c r="E125" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E125" s="19" t="s">
+      <c r="F125" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="F125" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G125" s="21" t="s">
-        <v>90</v>
       </c>
       <c r="H125" s="22" t="s">
         <v>17</v>
@@ -4377,19 +4359,19 @@
         <v>14.0</v>
       </c>
       <c r="C126" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D126" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D126" s="18" t="s">
+      <c r="E126" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E126" s="19" t="s">
-        <v>93</v>
-      </c>
       <c r="F126" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G126" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G126" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H126" s="22" t="s">
         <v>17</v>
@@ -4403,19 +4385,19 @@
         <v>15.0</v>
       </c>
       <c r="C127" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D127" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D127" s="18" t="s">
+      <c r="E127" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E127" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="F127" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G127" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H127" s="22" t="s">
         <v>17</v>
@@ -4429,19 +4411,19 @@
         <v>16.0</v>
       </c>
       <c r="C128" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D128" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D128" s="18" t="s">
+      <c r="E128" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E128" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="F128" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G128" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G128" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H128" s="22" t="s">
         <v>17</v>
@@ -4455,19 +4437,19 @@
         <v>17.0</v>
       </c>
       <c r="C129" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D129" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D129" s="18" t="s">
+      <c r="E129" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E129" s="19" t="s">
-        <v>102</v>
-      </c>
       <c r="F129" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G129" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H129" s="22" t="s">
         <v>17</v>
@@ -4499,11 +4481,11 @@
     </row>
     <row r="132" ht="15.0" customHeight="true">
       <c r="A132" s="39" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B132" s="40"/>
       <c r="C132" s="41" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D132" s="42"/>
       <c r="E132" s="43"/>
@@ -4571,19 +4553,19 @@
         <v>1.0</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F135" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G135" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H135" s="22" t="s">
         <v>17</v>
@@ -4623,19 +4605,19 @@
         <v>1.0</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D137" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E137" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F137" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G137" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H137" s="22" t="s">
         <v>17</v>
@@ -4667,11 +4649,11 @@
     </row>
     <row r="140" ht="15.0" customHeight="true">
       <c r="A140" s="39" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B140" s="40"/>
       <c r="C140" s="41" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D140" s="42"/>
       <c r="E140" s="43"/>
@@ -4765,19 +4747,19 @@
         <v>2.0</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D144" s="18" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E144" s="19" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F144" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G144" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H144" s="22" t="s">
         <v>17</v>
@@ -4817,19 +4799,19 @@
         <v>1.0</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D146" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E146" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F146" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G146" s="21" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H146" s="22" t="s">
         <v>17</v>
@@ -4861,11 +4843,11 @@
     </row>
     <row r="149" ht="15.0" customHeight="true">
       <c r="A149" s="39" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B149" s="40"/>
       <c r="C149" s="41" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D149" s="42"/>
       <c r="E149" s="43"/>
@@ -4933,19 +4915,19 @@
         <v>1.0</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D152" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E152" s="19" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F152" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G152" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G152" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H152" s="22" t="s">
         <v>17</v>
@@ -4985,19 +4967,19 @@
         <v>1.0</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D154" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E154" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F154" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G154" s="21" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H154" s="22" t="s">
         <v>17</v>
@@ -5029,11 +5011,11 @@
     </row>
     <row r="157" ht="15.0" customHeight="true">
       <c r="A157" s="39" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B157" s="40"/>
       <c r="C157" s="41" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D157" s="42"/>
       <c r="E157" s="43"/>
@@ -5153,19 +5135,19 @@
         <v>1.0</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D162" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E162" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F162" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G162" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H162" s="22" t="s">
         <v>17</v>
@@ -5197,11 +5179,11 @@
     </row>
     <row r="165" ht="15.0" customHeight="true">
       <c r="A165" s="39" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B165" s="40"/>
       <c r="C165" s="41" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D165" s="42"/>
       <c r="E165" s="43"/>
@@ -5269,19 +5251,19 @@
         <v>1.0</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E168" s="19" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F168" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G168" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H168" s="22" t="s">
         <v>17</v>
@@ -5295,19 +5277,19 @@
         <v>2.0</v>
       </c>
       <c r="C169" s="17" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D169" s="18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E169" s="19" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F169" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G169" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H169" s="22" t="s">
         <v>17</v>
@@ -5356,10 +5338,10 @@
         <v>42</v>
       </c>
       <c r="F171" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G171" s="21" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H171" s="22" t="s">
         <v>17</v>
@@ -5373,13 +5355,13 @@
         <v>2.0</v>
       </c>
       <c r="C172" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D172" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D172" s="18" t="s">
+      <c r="E172" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E172" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F172" s="20" t="s">
         <v>37</v>
@@ -5399,19 +5381,19 @@
         <v>3.0</v>
       </c>
       <c r="C173" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D173" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D173" s="18" t="s">
+      <c r="E173" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E173" s="19" t="s">
+      <c r="F173" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G173" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="F173" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G173" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H173" s="22" t="s">
         <v>17</v>
@@ -5425,19 +5407,19 @@
         <v>4.0</v>
       </c>
       <c r="C174" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D174" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D174" s="18" t="s">
+      <c r="E174" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E174" s="19" t="s">
+      <c r="F174" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F174" s="20" t="s">
+      <c r="G174" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G174" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H174" s="22" t="s">
         <v>17</v>
@@ -5451,19 +5433,19 @@
         <v>5.0</v>
       </c>
       <c r="C175" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D175" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D175" s="18" t="s">
+      <c r="E175" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E175" s="19" t="s">
-        <v>58</v>
-      </c>
       <c r="F175" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G175" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G175" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H175" s="22" t="s">
         <v>17</v>
@@ -5477,19 +5459,19 @@
         <v>6.0</v>
       </c>
       <c r="C176" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D176" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D176" s="18" t="s">
+      <c r="E176" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E176" s="19" t="s">
-        <v>61</v>
-      </c>
       <c r="F176" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G176" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G176" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H176" s="22" t="s">
         <v>17</v>
@@ -5503,19 +5485,19 @@
         <v>7.0</v>
       </c>
       <c r="C177" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D177" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D177" s="18" t="s">
+      <c r="E177" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E177" s="19" t="s">
-        <v>64</v>
-      </c>
       <c r="F177" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G177" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G177" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H177" s="22" t="s">
         <v>17</v>
@@ -5529,19 +5511,19 @@
         <v>8.0</v>
       </c>
       <c r="C178" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D178" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D178" s="18" t="s">
+      <c r="E178" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E178" s="19" t="s">
+      <c r="F178" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F178" s="20" t="s">
+      <c r="G178" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="G178" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="H178" s="22" t="s">
         <v>17</v>
@@ -5555,19 +5537,19 @@
         <v>9.0</v>
       </c>
       <c r="C179" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D179" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D179" s="18" t="s">
+      <c r="E179" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E179" s="19" t="s">
+      <c r="F179" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G179" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="F179" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G179" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="H179" s="22" t="s">
         <v>17</v>
@@ -5581,19 +5563,19 @@
         <v>10.0</v>
       </c>
       <c r="C180" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D180" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D180" s="18" t="s">
+      <c r="E180" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E180" s="19" t="s">
+      <c r="F180" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G180" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="F180" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G180" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H180" s="22" t="s">
         <v>17</v>
@@ -5607,19 +5589,19 @@
         <v>11.0</v>
       </c>
       <c r="C181" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D181" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D181" s="18" t="s">
+      <c r="E181" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E181" s="19" t="s">
+      <c r="F181" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G181" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F181" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G181" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H181" s="22" t="s">
         <v>17</v>
@@ -5633,19 +5615,19 @@
         <v>12.0</v>
       </c>
       <c r="C182" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D182" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D182" s="18" t="s">
+      <c r="E182" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E182" s="19" t="s">
+      <c r="F182" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F182" s="20" t="s">
+      <c r="G182" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="G182" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="H182" s="22" t="s">
         <v>17</v>
@@ -5659,19 +5641,19 @@
         <v>13.0</v>
       </c>
       <c r="C183" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D183" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D183" s="18" t="s">
+      <c r="E183" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E183" s="19" t="s">
+      <c r="F183" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G183" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="F183" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G183" s="21" t="s">
-        <v>90</v>
       </c>
       <c r="H183" s="22" t="s">
         <v>17</v>
@@ -5685,19 +5667,19 @@
         <v>14.0</v>
       </c>
       <c r="C184" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D184" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D184" s="18" t="s">
+      <c r="E184" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E184" s="19" t="s">
-        <v>93</v>
-      </c>
       <c r="F184" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G184" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G184" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H184" s="22" t="s">
         <v>17</v>
@@ -5711,19 +5693,19 @@
         <v>15.0</v>
       </c>
       <c r="C185" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D185" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D185" s="18" t="s">
+      <c r="E185" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E185" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="F185" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G185" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H185" s="22" t="s">
         <v>17</v>
@@ -5737,19 +5719,19 @@
         <v>16.0</v>
       </c>
       <c r="C186" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D186" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D186" s="18" t="s">
+      <c r="E186" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E186" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="F186" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G186" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G186" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H186" s="22" t="s">
         <v>17</v>
@@ -5763,19 +5745,19 @@
         <v>17.0</v>
       </c>
       <c r="C187" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D187" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D187" s="18" t="s">
+      <c r="E187" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E187" s="19" t="s">
-        <v>102</v>
-      </c>
       <c r="F187" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G187" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H187" s="22" t="s">
         <v>17</v>
@@ -5793,13 +5775,13 @@
     </row>
     <row r="189" ht="15.0" customHeight="true">
       <c r="A189" s="71" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B189" s="72" t="s">
         <v>17</v>
       </c>
       <c r="C189" s="73" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D189" s="74"/>
       <c r="E189" s="75"/>
@@ -5809,22 +5791,22 @@
     </row>
     <row r="190">
       <c r="A190" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="194">
@@ -5834,27 +5816,27 @@
     </row>
     <row r="195">
       <c r="A195" s="14" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="14" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="200">
@@ -5864,7 +5846,7 @@
     </row>
     <row r="201">
       <c r="A201" s="14" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
